--- a/artfynd/A 20949-2022 artfynd.xlsx
+++ b/artfynd/A 20949-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20949-2022 artfynd.xlsx
+++ b/artfynd/A 20949-2022 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>126877532</v>
       </c>
       <c r="B12" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>126877535</v>
       </c>
       <c r="B24" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 20949-2022 artfynd.xlsx
+++ b/artfynd/A 20949-2022 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>126877532</v>
       </c>
       <c r="B12" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>126877535</v>
       </c>
       <c r="B24" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 20949-2022 artfynd.xlsx
+++ b/artfynd/A 20949-2022 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>126877532</v>
       </c>
       <c r="B12" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>126877535</v>
       </c>
       <c r="B24" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 20949-2022 artfynd.xlsx
+++ b/artfynd/A 20949-2022 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>126877532</v>
       </c>
       <c r="B12" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>126877535</v>
       </c>
       <c r="B24" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 20949-2022 artfynd.xlsx
+++ b/artfynd/A 20949-2022 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>126877532</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>126877535</v>
       </c>
       <c r="B24" t="n">
-        <v>80123</v>
+        <v>80114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 20949-2022 artfynd.xlsx
+++ b/artfynd/A 20949-2022 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>126877532</v>
       </c>
       <c r="B12" t="n">
-        <v>80114</v>
+        <v>80123</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>126877535</v>
       </c>
       <c r="B24" t="n">
-        <v>80114</v>
+        <v>80123</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 20949-2022 artfynd.xlsx
+++ b/artfynd/A 20949-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111064923</v>
+        <v>111066345</v>
       </c>
       <c r="B2" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573149.9555546042</v>
+        <v>573143</v>
       </c>
       <c r="R2" t="n">
-        <v>7025869.367079071</v>
+        <v>7025881</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -775,6 +770,21 @@
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,15 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111065854</v>
+        <v>111064892</v>
       </c>
       <c r="B3" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573326.5380335175</v>
+        <v>573163</v>
       </c>
       <c r="R3" t="n">
-        <v>7025835.680528511</v>
+        <v>7025880</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -891,21 +896,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -922,15 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111065698</v>
+        <v>111064917</v>
       </c>
       <c r="B4" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -965,10 +950,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573125.2787711094</v>
+        <v>573216</v>
       </c>
       <c r="R4" t="n">
-        <v>7025867.008111101</v>
+        <v>7025891</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1022,21 +1007,6 @@
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1053,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111065736</v>
+        <v>111064923</v>
       </c>
       <c r="B5" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1069,21 +1034,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1096,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573150.3855442057</v>
+        <v>573150</v>
       </c>
       <c r="R5" t="n">
-        <v>7025850.517225829</v>
+        <v>7025870</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1153,21 +1118,6 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1184,15 +1134,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111064711</v>
+        <v>111064931</v>
       </c>
       <c r="B6" t="n">
-        <v>77516</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,21 +1145,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1227,10 +1172,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573079.7773476443</v>
+        <v>573172</v>
       </c>
       <c r="R6" t="n">
-        <v>7025811.636754569</v>
+        <v>7025831</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1300,15 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111066042</v>
+        <v>111064884</v>
       </c>
       <c r="B7" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1316,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1343,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573149.9484549079</v>
+        <v>573163</v>
       </c>
       <c r="R7" t="n">
-        <v>7025810.542368709</v>
+        <v>7025880</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1400,21 +1340,6 @@
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1434,12 +1359,7 @@
         <v>111065008</v>
       </c>
       <c r="B8" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,10 +1394,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573061.239095869</v>
+        <v>573061</v>
       </c>
       <c r="R8" t="n">
-        <v>7025796.395798424</v>
+        <v>7025797</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1562,15 +1482,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111064931</v>
+        <v>111065119</v>
       </c>
       <c r="B9" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,21 +1493,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1605,10 +1520,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>573171.5195016969</v>
+        <v>573083</v>
       </c>
       <c r="R9" t="n">
-        <v>7025830.792481128</v>
+        <v>7025864</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1662,6 +1577,21 @@
       <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1678,15 +1608,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111065936</v>
+        <v>111065252</v>
       </c>
       <c r="B10" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,10 +1646,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>573263.0230503018</v>
+        <v>573091</v>
       </c>
       <c r="R10" t="n">
-        <v>7025880.030978216</v>
+        <v>7025858</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1781,17 +1706,17 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>vanlig sälg</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Salix caprea subsp. caprea</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Salix caprea subsp. caprea</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1809,15 +1734,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111064642</v>
+        <v>111065549</v>
       </c>
       <c r="B11" t="n">
-        <v>77516</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1825,21 +1745,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1852,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>573050.6684824942</v>
+        <v>573128</v>
       </c>
       <c r="R11" t="n">
-        <v>7025747.208408665</v>
+        <v>7025852</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1909,6 +1829,21 @@
       <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1925,10 +1860,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126877532</v>
+        <v>111065698</v>
       </c>
       <c r="B12" t="n">
-        <v>80123</v>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1954,19 +1889,22 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Tallberget, Ång</t>
+          <t>Björnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>573092</v>
+        <v>573125</v>
       </c>
       <c r="R12" t="n">
-        <v>7025857</v>
+        <v>7025867</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1990,12 +1928,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2004,37 +1952,44 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Matthias Gustafsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111064540</v>
+        <v>111065711</v>
       </c>
       <c r="B13" t="n">
-        <v>77516</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2042,21 +1997,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2069,10 +2024,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>573312.4131708726</v>
+        <v>573146</v>
       </c>
       <c r="R13" t="n">
-        <v>7025922.470968609</v>
+        <v>7025862</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2142,15 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111065549</v>
+        <v>111065736</v>
       </c>
       <c r="B14" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2185,10 +2135,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>573128.3129986579</v>
+        <v>573150</v>
       </c>
       <c r="R14" t="n">
-        <v>7025852.259002013</v>
+        <v>7025850</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2273,15 +2223,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111066168</v>
+        <v>111065771</v>
       </c>
       <c r="B15" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2316,10 +2261,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>573125.6276368793</v>
+        <v>573202</v>
       </c>
       <c r="R15" t="n">
-        <v>7025831.99088038</v>
+        <v>7025912</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2404,15 +2349,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111066319</v>
+        <v>111065804</v>
       </c>
       <c r="B16" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2420,31 +2360,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2452,10 +2387,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>573108.4159333202</v>
+        <v>573303</v>
       </c>
       <c r="R16" t="n">
-        <v>7025857.193803206</v>
+        <v>7025813</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2506,22 +2441,23 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>vanlig gran</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Picea abies subsp. abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2539,15 +2475,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111064892</v>
+        <v>111065854</v>
       </c>
       <c r="B17" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2555,21 +2486,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2582,10 +2513,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>573162.7632614074</v>
+        <v>573326</v>
       </c>
       <c r="R17" t="n">
-        <v>7025879.538092798</v>
+        <v>7025836</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2639,6 +2570,21 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2655,15 +2601,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111064600</v>
+        <v>111065936</v>
       </c>
       <c r="B18" t="n">
-        <v>77516</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2671,21 +2612,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2698,10 +2639,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>573143.6975038678</v>
+        <v>573263</v>
       </c>
       <c r="R18" t="n">
-        <v>7025808.603599458</v>
+        <v>7025880</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2755,6 +2696,21 @@
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2771,15 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111064884</v>
+        <v>111066042</v>
       </c>
       <c r="B19" t="n">
-        <v>78107</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2787,21 +2738,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2814,10 +2765,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>573162.7632614074</v>
+        <v>573150</v>
       </c>
       <c r="R19" t="n">
-        <v>7025879.538092798</v>
+        <v>7025811</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2871,6 +2822,21 @@
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2887,15 +2853,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111065711</v>
+        <v>111066168</v>
       </c>
       <c r="B20" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2930,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>573146.0643958563</v>
+        <v>573125</v>
       </c>
       <c r="R20" t="n">
-        <v>7025862.542738394</v>
+        <v>7025832</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2987,6 +2948,21 @@
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3003,15 +2979,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111064917</v>
+        <v>111066179</v>
       </c>
       <c r="B21" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3019,21 +2990,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3046,10 +3017,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>573215.9973113885</v>
+        <v>573082</v>
       </c>
       <c r="R21" t="n">
-        <v>7025891.529964242</v>
+        <v>7025813</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3103,6 +3074,21 @@
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3119,15 +3105,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111066179</v>
+        <v>126877532</v>
       </c>
       <c r="B22" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3153,22 +3134,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Björnbäcken, Ång</t>
+          <t>Tallberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>573082.003996659</v>
+        <v>573092</v>
       </c>
       <c r="R22" t="n">
-        <v>7025812.585589756</v>
+        <v>7025857</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3192,22 +3170,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3216,49 +3184,32 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Matthias Gustafsson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Matthias Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111066304</v>
+        <v>126877535</v>
       </c>
       <c r="B23" t="n">
-        <v>56398</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3266,45 +3217,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Björnbäcken, Ång</t>
+          <t>Tallberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>573269.6701411926</v>
+        <v>573161</v>
       </c>
       <c r="R23" t="n">
-        <v>7025903.981754016</v>
+        <v>7025858</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3328,22 +3271,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>16:00</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-07-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>18:30</t>
+          <t>2025-07-19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3354,41 +3287,30 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Matthias Gustafsson</t>
+          <t>Ulrika Westling</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Matthias Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Ulrika Westling</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126877535</v>
+        <v>111066304</v>
       </c>
       <c r="B24" t="n">
-        <v>80123</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,37 +3318,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Tallberget, Ång</t>
+          <t>Björnbäcken, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>573161</v>
+        <v>573269</v>
       </c>
       <c r="R24" t="n">
-        <v>7025858</v>
+        <v>7025904</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3450,12 +3380,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-07-19</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3466,23 +3406,849 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
+          <t>Matthias Gustafsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Ulrika Westling</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>111066319</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Björnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>573108</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7025857</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>111066329</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Björnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>573078</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7025872</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>111064540</v>
+      </c>
+      <c r="B27" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Björnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>573313</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7025923</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>111064600</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Björnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>573144</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7025808</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>111064642</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Björnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>573051</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7025747</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>111064711</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Björnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>573080</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7025812</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>111064773</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79328</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>230405</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav (ssp. sarmentosa)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Björnbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>573191</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7025902</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Edsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Matthias Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20949-2022 artfynd.xlsx
+++ b/artfynd/A 20949-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AZ31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111066345</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111064892</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111064917</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111064923</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1242,6 +1267,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111064931</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111064884</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1479,6 +1514,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065008</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1605,6 +1645,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065119</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1731,6 +1776,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065252</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1857,6 +1907,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065549</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1983,6 +2038,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065698</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2094,6 +2154,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065711</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2220,6 +2285,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065736</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2346,6 +2416,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065771</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2472,6 +2547,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065804</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2598,6 +2678,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065854</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2724,6 +2809,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111065936</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2850,6 +2940,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111066042</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2976,6 +3071,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111066168</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3102,6 +3202,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111066179</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3203,6 +3308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126877532</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3304,6 +3414,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126877535</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3434,6 +3549,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111066304</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3564,6 +3684,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111066319</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3694,6 +3819,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111066329</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3805,6 +3935,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111064540</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3916,6 +4051,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111064600</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4027,6 +4167,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111064642</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4138,6 +4283,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111064711</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4249,8 +4399,45 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111064773</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>